--- a/data/Program Data.xlsx
+++ b/data/Program Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s2730428\Documents\GTF\global-talent-map\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Documents\GTF-Impact-Map\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DE2AFB-BBFF-490D-84AC-17E3D8888327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC3E499-50CC-4FFF-807E-9C58A6B32A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AD56EADB-1935-49BD-AB38-7127B858C65A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AD56EADB-1935-49BD-AB38-7127B858C65A}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t>Country</t>
   </si>
@@ -70,9 +67,6 @@
   </si>
   <si>
     <t>Mongolia</t>
-  </si>
-  <si>
-    <t>East Africa</t>
   </si>
   <si>
     <t>Bolivia</t>
@@ -323,10 +317,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}" name="Table1" displayName="Table1" ref="A1:D74" totalsRowShown="0">
-  <autoFilter ref="A1:D74" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D74">
-    <sortCondition ref="A1:A74"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}" name="Table1" displayName="Table1" ref="A1:D73" totalsRowShown="0">
+  <autoFilter ref="A1:D73" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D73">
+    <sortCondition ref="A1:A73"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{BB1A4DB9-2749-4819-BDEB-2476FD66E4FC}" name="Country"/>
@@ -339,9 +333,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -379,7 +373,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -485,7 +479,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -627,7 +621,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -635,14 +629,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6A2811-651E-4A40-8F1F-EACB1DE63CE0}">
-  <dimension ref="A1:D74"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D73"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.1796875" customWidth="1"/>
-    <col min="2" max="2" width="10.36328125" customWidth="1"/>
+    <col min="1" max="1" width="34.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -656,220 +650,220 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>37</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>38</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>31</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>39</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>40</v>
-      </c>
       <c r="B17">
         <v>0</v>
       </c>
@@ -880,7 +874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -894,161 +888,161 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>41</v>
       </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>65</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>43</v>
       </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>13</v>
-      </c>
       <c r="B29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -1059,10 +1053,10 @@
         <v>1</v>
       </c>
       <c r="D30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>45</v>
       </c>
@@ -1073,10 +1067,10 @@
         <v>1</v>
       </c>
       <c r="D31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -1090,119 +1084,119 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>67</v>
       </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>76</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>21</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>29</v>
-      </c>
       <c r="B40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>68</v>
       </c>
@@ -1216,175 +1210,175 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>27</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>69</v>
       </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>28</v>
-      </c>
       <c r="B43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>70</v>
       </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>7</v>
-      </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46">
-        <v>1</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>22</v>
-      </c>
-      <c r="B47">
-        <v>1</v>
-      </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>10</v>
-      </c>
       <c r="B48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>16</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>47</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>71</v>
       </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-      <c r="D49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>17</v>
-      </c>
-      <c r="B50">
-        <v>1</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>48</v>
       </c>
-      <c r="B51">
-        <v>0</v>
-      </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>18</v>
-      </c>
-      <c r="B52">
-        <v>1</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>72</v>
-      </c>
       <c r="B53">
         <v>0</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>49</v>
       </c>
@@ -1395,94 +1389,94 @@
         <v>1</v>
       </c>
       <c r="D54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>50</v>
       </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>20</v>
-      </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>9</v>
-      </c>
       <c r="B57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>51</v>
       </c>
-      <c r="B58">
-        <v>0</v>
-      </c>
-      <c r="C58">
-        <v>1</v>
-      </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>26</v>
-      </c>
-      <c r="B59">
-        <v>1</v>
-      </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>6</v>
-      </c>
       <c r="B60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60">
         <v>1</v>
       </c>
       <c r="D60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>52</v>
       </c>
@@ -1496,40 +1490,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>53</v>
       </c>
-      <c r="B62">
-        <v>0</v>
-      </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>14</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
-      </c>
-      <c r="C63">
-        <v>1</v>
-      </c>
-      <c r="D63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>5</v>
-      </c>
       <c r="B64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -1538,7 +1532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>54</v>
       </c>
@@ -1549,10 +1543,10 @@
         <v>1</v>
       </c>
       <c r="D65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>55</v>
       </c>
@@ -1566,7 +1560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>56</v>
       </c>
@@ -1577,10 +1571,10 @@
         <v>1</v>
       </c>
       <c r="D67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>57</v>
       </c>
@@ -1591,24 +1585,24 @@
         <v>1</v>
       </c>
       <c r="D68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B69">
         <v>0</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -1622,65 +1616,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>59</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>35</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>74</v>
       </c>
-      <c r="B71">
-        <v>0</v>
-      </c>
-      <c r="C71">
-        <v>0</v>
-      </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>60</v>
-      </c>
-      <c r="B72">
-        <v>0</v>
-      </c>
-      <c r="C72">
-        <v>1</v>
-      </c>
-      <c r="D72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>36</v>
-      </c>
       <c r="B73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>75</v>
-      </c>
-      <c r="B74">
-        <v>0</v>
-      </c>
-      <c r="C74">
-        <v>0</v>
-      </c>
-      <c r="D74">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A35">
-    <sortCondition ref="A2:A35"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A34">
+    <sortCondition ref="A2:A34"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/Program Data.xlsx
+++ b/data/Program Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Documents\GTF-Impact-Map\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s2730428\Documents\GTF-Impact-Map\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC3E499-50CC-4FFF-807E-9C58A6B32A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739ACBF5-638A-404E-AC54-839D33172FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AD56EADB-1935-49BD-AB38-7127B858C65A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AD56EADB-1935-49BD-AB38-7127B858C65A}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>Country</t>
   </si>
@@ -262,6 +265,9 @@
   </si>
   <si>
     <t>Ivory Coast</t>
+  </si>
+  <si>
+    <t>Portugal</t>
   </si>
 </sst>
 </file>
@@ -317,10 +323,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}" name="Table1" displayName="Table1" ref="A1:D73" totalsRowShown="0">
-  <autoFilter ref="A1:D73" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D73">
-    <sortCondition ref="A1:A73"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}" name="Table1" displayName="Table1" ref="A1:D74" totalsRowShown="0">
+  <autoFilter ref="A1:D74" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D74">
+    <sortCondition ref="A1:A74"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{BB1A4DB9-2749-4819-BDEB-2476FD66E4FC}" name="Country"/>
@@ -333,9 +339,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -373,7 +379,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -479,7 +485,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -621,7 +627,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -629,14 +635,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6A2811-651E-4A40-8F1F-EACB1DE63CE0}">
-  <dimension ref="A1:D73"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D74"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="34.1796875" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -650,7 +656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -664,7 +670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -678,7 +684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>60</v>
       </c>
@@ -692,7 +698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -706,7 +712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -720,7 +726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>61</v>
       </c>
@@ -734,7 +740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -748,7 +754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -762,7 +768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -776,7 +782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -790,7 +796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -804,7 +810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -818,7 +824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -832,7 +838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -846,7 +852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -860,7 +866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -874,7 +880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -888,7 +894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -902,7 +908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>64</v>
       </c>
@@ -916,7 +922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -930,7 +936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -944,7 +950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -958,7 +964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -972,7 +978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>65</v>
       </c>
@@ -986,7 +992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1000,7 +1006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -1014,7 +1020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -1028,7 +1034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -1042,7 +1048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -1056,7 +1062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>45</v>
       </c>
@@ -1070,7 +1076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -1084,7 +1090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -1098,7 +1104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -1112,7 +1118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>75</v>
       </c>
@@ -1126,7 +1132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>20</v>
       </c>
@@ -1140,7 +1146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>34</v>
       </c>
@@ -1154,7 +1160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -1168,7 +1174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -1182,7 +1188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>67</v>
       </c>
@@ -1196,7 +1202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>68</v>
       </c>
@@ -1210,7 +1216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -1224,7 +1230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>69</v>
       </c>
@@ -1238,7 +1244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -1252,7 +1258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -1266,7 +1272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>21</v>
       </c>
@@ -1280,7 +1286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>10</v>
       </c>
@@ -1294,7 +1300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>70</v>
       </c>
@@ -1308,7 +1314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>16</v>
       </c>
@@ -1322,7 +1328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>47</v>
       </c>
@@ -1336,7 +1342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>17</v>
       </c>
@@ -1350,7 +1356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>71</v>
       </c>
@@ -1364,7 +1370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1378,7 +1384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>49</v>
       </c>
@@ -1392,7 +1398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>19</v>
       </c>
@@ -1406,7 +1412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -1420,7 +1426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>50</v>
       </c>
@@ -1434,7 +1440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -1448,7 +1454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -1462,199 +1468,213 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>76</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>51</v>
       </c>
-      <c r="B60">
-        <v>0</v>
-      </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-      <c r="D60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>52</v>
       </c>
-      <c r="B61">
-        <v>0</v>
-      </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>13</v>
       </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>5</v>
       </c>
-      <c r="B63">
-        <v>1</v>
-      </c>
-      <c r="C63">
-        <v>1</v>
-      </c>
-      <c r="D63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="B64">
+        <v>1</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>53</v>
       </c>
-      <c r="B64">
-        <v>0</v>
-      </c>
-      <c r="C64">
-        <v>1</v>
-      </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>54</v>
       </c>
-      <c r="B65">
-        <v>0</v>
-      </c>
-      <c r="C65">
-        <v>1</v>
-      </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>55</v>
       </c>
-      <c r="B66">
-        <v>0</v>
-      </c>
-      <c r="C66">
-        <v>1</v>
-      </c>
-      <c r="D66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>56</v>
       </c>
-      <c r="B67">
-        <v>0</v>
-      </c>
-      <c r="C67">
-        <v>1</v>
-      </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>57</v>
       </c>
-      <c r="B68">
-        <v>0</v>
-      </c>
-      <c r="C68">
-        <v>1</v>
-      </c>
-      <c r="D68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>72</v>
       </c>
-      <c r="B69">
-        <v>0</v>
-      </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-      <c r="D69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>73</v>
       </c>
-      <c r="B70">
-        <v>0</v>
-      </c>
-      <c r="C70">
-        <v>0</v>
-      </c>
-      <c r="D70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>59</v>
       </c>
-      <c r="B71">
-        <v>0</v>
-      </c>
-      <c r="C71">
-        <v>1</v>
-      </c>
-      <c r="D71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>35</v>
       </c>
-      <c r="B72">
-        <v>1</v>
-      </c>
-      <c r="C72">
-        <v>1</v>
-      </c>
-      <c r="D72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>74</v>
       </c>
-      <c r="B73">
-        <v>0</v>
-      </c>
-      <c r="C73">
-        <v>0</v>
-      </c>
-      <c r="D73">
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
         <v>1</v>
       </c>
     </row>

--- a/data/Program Data.xlsx
+++ b/data/Program Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s2730428\Documents\GTF-Impact-Map\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739ACBF5-638A-404E-AC54-839D33172FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC75737-7286-45DB-9F7F-A73B885688CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AD56EADB-1935-49BD-AB38-7127B858C65A}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="7270" xr2:uid="{AD56EADB-1935-49BD-AB38-7127B858C65A}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>Country</t>
   </si>
@@ -267,7 +267,13 @@
     <t>Ivory Coast</t>
   </si>
   <si>
-    <t>Portugal</t>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Sri Lanka</t>
+  </si>
+  <si>
+    <t>Israel</t>
   </si>
 </sst>
 </file>
@@ -323,10 +329,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}" name="Table1" displayName="Table1" ref="A1:D74" totalsRowShown="0">
-  <autoFilter ref="A1:D74" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D74">
-    <sortCondition ref="A1:A74"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}" name="Table1" displayName="Table1" ref="A1:D76" totalsRowShown="0">
+  <autoFilter ref="A1:D76" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D76">
+    <sortCondition ref="A1:A76"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{BB1A4DB9-2749-4819-BDEB-2476FD66E4FC}" name="Country"/>
@@ -635,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6A2811-651E-4A40-8F1F-EACB1DE63CE0}">
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34.1796875" customWidth="1"/>
@@ -815,7 +821,7 @@
         <v>63</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -854,13 +860,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -868,13 +874,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -882,10 +888,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -896,13 +902,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -910,21 +916,21 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -933,15 +939,15 @@
         <v>1</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -952,10 +958,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -966,13 +972,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -980,21 +986,21 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -1008,35 +1014,35 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1045,12 +1051,12 @@
         <v>1</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1059,12 +1065,12 @@
         <v>1</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1078,55 +1084,55 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1134,7 +1140,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -1143,12 +1149,12 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -1162,13 +1168,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1176,13 +1182,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1190,7 +1196,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1204,27 +1210,27 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -1232,13 +1238,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1246,7 +1252,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -1260,7 +1266,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -1274,27 +1280,27 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -1302,13 +1308,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -1316,27 +1322,27 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49">
         <v>1</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -1344,35 +1350,35 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="B52">
         <v>0</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1381,15 +1387,15 @@
         <v>1</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -1400,7 +1406,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -1414,13 +1420,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -1428,21 +1434,21 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -1456,27 +1462,27 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59">
         <v>1</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -1484,38 +1490,38 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -1526,21 +1532,21 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64">
         <v>1</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1549,26 +1555,26 @@
         <v>1</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1582,13 +1588,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -1596,41 +1602,41 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B69">
         <v>0</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -1638,21 +1644,21 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -1666,21 +1672,49 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>35</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A34">
-    <sortCondition ref="A2:A34"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A33">
+    <sortCondition ref="A2:A33"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/Program Data.xlsx
+++ b/data/Program Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s2730428\Documents\GTF-Impact-Map\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\iona.sms.ed.ac.uk\home\s2730428\GTF-Impact-Map\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC75737-7286-45DB-9F7F-A73B885688CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0029E2-163D-44C9-9090-60223E397C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="7270" xr2:uid="{AD56EADB-1935-49BD-AB38-7127B858C65A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{AD56EADB-1935-49BD-AB38-7127B858C65A}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -123,9 +123,6 @@
     <t>Lithuania</t>
   </si>
   <si>
-    <t xml:space="preserve">Kyrgyzstan </t>
-  </si>
-  <si>
     <t>Bulgaria</t>
   </si>
   <si>
@@ -189,18 +186,12 @@
     <t>Nicaragua</t>
   </si>
   <si>
-    <t>Palestine</t>
-  </si>
-  <si>
     <t>Qatar</t>
   </si>
   <si>
     <t>Russian Federation</t>
   </si>
   <si>
-    <t>South Sudan</t>
-  </si>
-  <si>
     <t>Switzerland</t>
   </si>
   <si>
@@ -210,12 +201,6 @@
     <t>Tunisia</t>
   </si>
   <si>
-    <t>Turkey</t>
-  </si>
-  <si>
-    <t>Democratic Republic of the Congo</t>
-  </si>
-  <si>
     <t>United States of America</t>
   </si>
   <si>
@@ -274,6 +259,21 @@
   </si>
   <si>
     <t>Israel</t>
+  </si>
+  <si>
+    <t>Kyrgyz Republic</t>
+  </si>
+  <si>
+    <t>West Bank and Gaza</t>
+  </si>
+  <si>
+    <t>Congo, Dem. Rep. of the</t>
+  </si>
+  <si>
+    <t>South Sudan, Republic of</t>
+  </si>
+  <si>
+    <t>Türkiye, Republic of</t>
   </si>
 </sst>
 </file>
@@ -642,13 +642,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6A2811-651E-4A40-8F1F-EACB1DE63CE0}">
   <dimension ref="A1:D76"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.1796875" customWidth="1"/>
-    <col min="2" max="2" width="10.453125" customWidth="1"/>
+    <col min="1" max="1" width="34.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -662,24 +662,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>36</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>37</v>
-      </c>
       <c r="B3">
         <v>0</v>
       </c>
@@ -690,9 +690,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -704,9 +704,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -718,7 +718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -732,9 +732,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -746,9 +746,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -760,7 +760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -774,7 +774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -788,9 +788,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -802,7 +802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -816,9 +816,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -830,9 +830,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -844,9 +844,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -858,9 +858,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -872,7 +872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -886,52 +886,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>40</v>
       </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>41</v>
-      </c>
       <c r="B21">
         <v>0</v>
       </c>
@@ -942,7 +942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -956,9 +956,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -970,9 +970,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -984,9 +984,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -998,7 +998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1026,52 +1026,52 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>43</v>
       </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>44</v>
       </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>45</v>
       </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>46</v>
-      </c>
       <c r="B31">
         <v>0</v>
       </c>
@@ -1082,9 +1082,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1096,9 +1096,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -1110,9 +1110,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>12</v>
       </c>
@@ -1138,9 +1138,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -1152,9 +1152,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>20</v>
       </c>
@@ -1180,9 +1180,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1194,9 +1194,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1208,9 +1208,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -1222,9 +1222,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1236,7 +1236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -1250,9 +1250,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1292,9 +1292,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1306,7 +1306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -1320,9 +1320,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>21</v>
       </c>
@@ -1348,9 +1348,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1362,24 +1362,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>47</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>48</v>
       </c>
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>49</v>
-      </c>
       <c r="B53">
         <v>0</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>10</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>16</v>
       </c>
@@ -1418,9 +1418,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1432,7 +1432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -1460,9 +1460,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1474,9 +1474,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>25</v>
       </c>
@@ -1516,9 +1516,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1530,9 +1530,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1544,9 +1544,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>6</v>
       </c>
@@ -1572,9 +1572,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1586,9 +1586,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -1600,9 +1600,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1614,9 +1614,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>13</v>
       </c>
@@ -1642,9 +1642,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1656,7 +1656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>5</v>
       </c>
@@ -1670,9 +1670,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -1684,9 +1684,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -1698,9 +1698,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B76">
         <v>1</v>

--- a/data/Program Data.xlsx
+++ b/data/Program Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\iona.sms.ed.ac.uk\home\s2730428\GTF-Impact-Map\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Documents\Global Talent Fund\GTF-Impact-Map\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0029E2-163D-44C9-9090-60223E397C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E1933B-FF9C-420A-97E9-C9ED3A24C2C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{AD56EADB-1935-49BD-AB38-7127B858C65A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AD56EADB-1935-49BD-AB38-7127B858C65A}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>Country</t>
   </si>
@@ -109,12 +106,6 @@
   </si>
   <si>
     <t>Armenia</t>
-  </si>
-  <si>
-    <t>Egypt</t>
-  </si>
-  <si>
-    <t>Peru</t>
   </si>
   <si>
     <t>Chile</t>
@@ -329,10 +320,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}" name="Table1" displayName="Table1" ref="A1:D76" totalsRowShown="0">
-  <autoFilter ref="A1:D76" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D76">
-    <sortCondition ref="A1:A76"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}" name="Table1" displayName="Table1" ref="A1:D74" totalsRowShown="0">
+  <autoFilter ref="A1:D74" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D74">
+    <sortCondition ref="A1:A74"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{BB1A4DB9-2749-4819-BDEB-2476FD66E4FC}" name="Country"/>
@@ -345,9 +336,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -385,7 +376,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -491,7 +482,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -633,7 +624,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -641,8 +632,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6A2811-651E-4A40-8F1F-EACB1DE63CE0}">
-  <dimension ref="A1:D76"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D74"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.140625" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" customWidth="1"/>
@@ -664,7 +655,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -678,7 +669,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -692,7 +683,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -706,7 +697,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -734,7 +725,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -748,7 +739,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -790,7 +781,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -818,7 +809,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -832,7 +823,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -846,7 +837,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -860,7 +851,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -874,7 +865,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -888,7 +879,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -902,7 +893,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -916,7 +907,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -930,7 +921,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -958,7 +949,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -972,7 +963,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -986,7 +977,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -1000,7 +991,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -1014,21 +1005,21 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1037,12 +1028,12 @@
         <v>1</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1051,12 +1042,12 @@
         <v>1</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1070,55 +1061,55 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1126,21 +1117,21 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -1154,7 +1145,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -1163,15 +1154,15 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -1182,7 +1173,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1196,41 +1187,41 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -1238,7 +1229,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -1252,7 +1243,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -1266,7 +1257,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -1280,13 +1271,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -1294,13 +1285,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -1308,27 +1299,27 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48">
         <v>1</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -1336,35 +1327,35 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="B51">
         <v>0</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1373,15 +1364,15 @@
         <v>1</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -1392,7 +1383,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -1406,10 +1397,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -1420,21 +1411,21 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -1443,26 +1434,26 @@
         <v>1</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1476,27 +1467,27 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -1504,21 +1495,21 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1527,26 +1518,26 @@
         <v>1</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64">
         <v>1</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1560,13 +1551,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -1574,41 +1565,41 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -1616,21 +1607,21 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -1644,21 +1635,21 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -1672,49 +1663,21 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>53</v>
-      </c>
-      <c r="B75">
-        <v>1</v>
-      </c>
-      <c r="C75">
-        <v>1</v>
-      </c>
-      <c r="D75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>34</v>
-      </c>
-      <c r="B76">
-        <v>1</v>
-      </c>
-      <c r="C76">
-        <v>1</v>
-      </c>
-      <c r="D76">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A33">
-    <sortCondition ref="A2:A33"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A32">
+    <sortCondition ref="A2:A32"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/Program Data.xlsx
+++ b/data/Program Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Documents\Global Talent Fund\GTF-Impact-Map\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E1933B-FF9C-420A-97E9-C9ED3A24C2C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB83E6A-F119-47F7-8EFF-E4F7C49C4DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AD56EADB-1935-49BD-AB38-7127B858C65A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>Country</t>
   </si>
@@ -265,6 +265,12 @@
   </si>
   <si>
     <t>Türkiye, Republic of</t>
+  </si>
+  <si>
+    <t>Egypt</t>
+  </si>
+  <si>
+    <t>Peru</t>
   </si>
 </sst>
 </file>
@@ -320,8 +326,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}" name="Table1" displayName="Table1" ref="A1:D74" totalsRowShown="0">
-  <autoFilter ref="A1:D74" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}" name="Table1" displayName="Table1" ref="A1:D76" totalsRowShown="0">
+  <autoFilter ref="A1:D76" xr:uid="{7EBCA682-35F6-443E-9599-16C39EBD80EE}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D74">
     <sortCondition ref="A1:A74"/>
   </sortState>
@@ -632,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6A2811-651E-4A40-8F1F-EACB1DE63CE0}">
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.140625" customWidth="1"/>
@@ -1673,6 +1679,34 @@
       </c>
       <c r="D74">
         <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>78</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
